--- a/output/pdf_financials_xlsx/ADG.xlsx
+++ b/output/pdf_financials_xlsx/ADG.xlsx
@@ -2322,49 +2322,49 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.822214</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.085046</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09726799999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.070784</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021217</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.061344</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010542</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.388311</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.127626</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.028299</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010433</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.157748</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.079176</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.028032</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.000564</v>
       </c>
     </row>
     <row r="35">
@@ -2426,49 +2426,49 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.822214</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.085046</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.09726799999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.070784</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021217</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.061344</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010542</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.388311</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.127626</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.028299</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010433</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.157748</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.079176</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.028032</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.000564</v>
       </c>
     </row>
     <row r="37">
@@ -3056,19 +3056,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.120435</v>
+        <v>0.023167</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.074611</v>
+        <v>0.003827</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.029036</v>
+        <v>0.007819</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.061344</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.010542</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.011049</v>
+        <v>0.000616</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.157949</v>
+        <v>0.000201</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.080946</v>
+        <v>0.00177</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/output/pdf_financials_xlsx/ADG.xlsx
+++ b/output/pdf_financials_xlsx/ADG.xlsx
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.14</v>
+        <v>0.14</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.031</v>
+        <v>-0.031</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -26324,7 +26324,11 @@
           <t>Deferred income tax recovery (expense) 11, 12</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
